--- a/artfynd/A 8819-2024 artfynd.xlsx
+++ b/artfynd/A 8819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114742681</v>
+        <v>114742888</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rinkabynäset, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491260</v>
+        <v>491249</v>
       </c>
       <c r="R2" t="n">
-        <v>6294515</v>
+        <v>6294420</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,12 +780,7 @@
         <v>114742680</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116241263</v>
+        <v>114742681</v>
       </c>
       <c r="B4" t="n">
-        <v>96695</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,41 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rinkaby 3:3, Sm</t>
+          <t>Rinkabynäset, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491357</v>
+        <v>491260</v>
       </c>
       <c r="R4" t="n">
-        <v>6294376</v>
+        <v>6294515</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,22 +953,123 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116241263</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rinkaby 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6294376</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tävelsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Annica Pettersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Annica Pettersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8819-2024 artfynd.xlsx
+++ b/artfynd/A 8819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114742888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114742680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114742681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116241263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>